--- a/Training/Day3_Calibration/IO_Calibration/data/output/ModelCalibration5Sectorsand1Regions_IO_Data_Replaced.xlsx
+++ b/Training/Day3_Calibration/IO_Calibration/data/output/ModelCalibration5Sectorsand1Regions_IO_Data_Replaced.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC-VietNam\Training\Day3_Calibration\matlab_pipeline\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC-VietNam\Training\Day3_Calibration\IO_Calibration\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68972C5-C78D-4360-A168-D5A0ACB519AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF00937-FD12-49B5-8FBF-017C279100F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5421,6 +5421,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A39:C39"/>
@@ -5428,18 +5440,6 @@
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A27:C27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
